--- a/cn-med-kg/medicine_dataset.xlsx
+++ b/cn-med-kg/medicine_dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Chinese_Medicine\CM_Ref\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Chinese_Medicine\cn-med-kg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{81BAEAD5-7EB9-4D76-AEFC-681916D1333B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C279403B-CCAA-406C-8BD8-179DD8009012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-9998" windowWidth="28995" windowHeight="17476" activeTab="3" xr2:uid="{FCBB9041-7F32-418A-9A6B-AB2AB6A56C91}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{FCBB9041-7F32-418A-9A6B-AB2AB6A56C91}"/>
   </bookViews>
   <sheets>
     <sheet name="1-namelist" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="153">
   <si>
     <t>药品名称</t>
   </si>
@@ -342,13 +342,169 @@
   </si>
   <si>
     <t>药品ID</t>
+  </si>
+  <si>
+    <t>利口乐甜味口香糖</t>
+  </si>
+  <si>
+    <t>利口乐</t>
+  </si>
+  <si>
+    <t>BrandEnglish</t>
+  </si>
+  <si>
+    <t>NameEnglish</t>
+  </si>
+  <si>
+    <t>Ricola</t>
+  </si>
+  <si>
+    <t>ComponentEnglish</t>
+  </si>
+  <si>
+    <t>m000006</t>
+  </si>
+  <si>
+    <t>白毛茛</t>
+  </si>
+  <si>
+    <t>伯内特</t>
+  </si>
+  <si>
+    <t>速生草</t>
+  </si>
+  <si>
+    <t>棉花糖植物</t>
+  </si>
+  <si>
+    <t>女士斗篷</t>
+  </si>
+  <si>
+    <t>接骨木花</t>
+  </si>
+  <si>
+    <t>锦葵</t>
+  </si>
+  <si>
+    <t>圣人</t>
+  </si>
+  <si>
+    <t>蓍草</t>
+  </si>
+  <si>
+    <t>报春花</t>
+  </si>
+  <si>
+    <t>芭蕉</t>
+  </si>
+  <si>
+    <t>百里香</t>
+  </si>
+  <si>
+    <t>Horehound</t>
+  </si>
+  <si>
+    <t>Burnet</t>
+  </si>
+  <si>
+    <t>Speedwell</t>
+  </si>
+  <si>
+    <t>Marshmallow Plant</t>
+  </si>
+  <si>
+    <t>Lady's Mantle</t>
+  </si>
+  <si>
+    <t>Elderflower</t>
+  </si>
+  <si>
+    <t>Mallow</t>
+  </si>
+  <si>
+    <t>Peppermint</t>
+  </si>
+  <si>
+    <t>Sage</t>
+  </si>
+  <si>
+    <t>Yarrow</t>
+  </si>
+  <si>
+    <t>Cowslip</t>
+  </si>
+  <si>
+    <t>Plantain</t>
+  </si>
+  <si>
+    <t>Thyme</t>
+  </si>
+  <si>
+    <t>Ricola Herbal Drops</t>
+  </si>
+  <si>
+    <t>生产商网址</t>
+  </si>
+  <si>
+    <t>https://www.ricola.com/</t>
+  </si>
+  <si>
+    <t>Ricola Group AG</t>
+  </si>
+  <si>
+    <t>Baslestrasse 31, 4242 Laufen, Switzerland</t>
+  </si>
+  <si>
+    <t>+41 61 765 41 21</t>
+  </si>
+  <si>
+    <t>强力枇杷露</t>
+  </si>
+  <si>
+    <t>胡庆余堂</t>
+  </si>
+  <si>
+    <t>杭州胡庆余堂药业有限公司</t>
+  </si>
+  <si>
+    <t>浙江杭州</t>
+  </si>
+  <si>
+    <t>m000007</t>
+  </si>
+  <si>
+    <t>枇杷叶</t>
+  </si>
+  <si>
+    <t>罂粟壳</t>
+  </si>
+  <si>
+    <t>百部</t>
+  </si>
+  <si>
+    <t>白前</t>
+  </si>
+  <si>
+    <t>桑白皮</t>
+  </si>
+  <si>
+    <t>桔梗</t>
+  </si>
+  <si>
+    <t>养阴敛肺</t>
+  </si>
+  <si>
+    <t>止咳祛痰</t>
+  </si>
+  <si>
+    <t>支气管炎咳嗽</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,6 +514,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -476,19 +640,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -498,181 +669,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
+  <dxfs count="35">
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -725,6 +735,36 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -808,13 +848,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -830,11 +863,11 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border outline="0">
@@ -844,22 +877,11 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -883,8 +905,34 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -899,26 +947,23 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
         <top style="thin">
           <color indexed="64"/>
         </top>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -931,6 +976,296 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -949,51 +1284,55 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}" name="Table2" displayName="Table2" ref="A1:G6" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G6" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{70404F4C-EA74-419B-B8F7-C0E749DBA8EF}" name="药品名称" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{A127C5AC-1A8D-4194-B82B-CEA8C46568A9}" name="UID" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}" name="Table2" displayName="Table2" ref="A1:J8" totalsRowShown="0" headerRowDxfId="34" headerRowBorderDxfId="33" tableBorderDxfId="32" totalsRowBorderDxfId="31">
+  <autoFilter ref="A1:J8" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{70404F4C-EA74-419B-B8F7-C0E749DBA8EF}" name="药品名称" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{A127C5AC-1A8D-4194-B82B-CEA8C46568A9}" name="UID" dataDxfId="29">
       <calculatedColumnFormula>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{745BAE8D-3E74-492D-9F1F-A46F418B7407}" name="品牌" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{21E7B030-7D6F-4754-8BAA-1C33EF145001}" name="生产商" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{76794CF7-5E96-4BA4-A111-0F4FB586AAEB}" name="生产商地址" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{098A7009-4AD7-411F-A1F5-1CE1E004D519}" name="生产商电话" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{2B5D44FA-F4F3-4890-8993-4D8C1FD7AA21}" name="执行标准" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{745BAE8D-3E74-492D-9F1F-A46F418B7407}" name="品牌" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{4568304F-01F3-4E31-A34C-C35C96C88C80}" name="NameEnglish" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{8640C111-58A7-4B70-8A2F-6ECA558B9042}" name="BrandEnglish" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{21E7B030-7D6F-4754-8BAA-1C33EF145001}" name="生产商" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{76794CF7-5E96-4BA4-A111-0F4FB586AAEB}" name="生产商地址" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{835D09B6-5D13-418C-9FB4-33A768C770CA}" name="生产商网址" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{098A7009-4AD7-411F-A1F5-1CE1E004D519}" name="生产商电话" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{2B5D44FA-F4F3-4890-8993-4D8C1FD7AA21}" name="执行标准" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}" name="Table3" displayName="Table3" ref="A1:B60" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="29" tableBorderDxfId="30" totalsRowBorderDxfId="28">
-  <autoFilter ref="A1:B60" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9CBDF56B-3BCD-4FF2-8195-561FA1F4C31A}" name="药品ID" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{77270F8D-0C55-4EBC-B9E0-6E3C41859F9D}" name="成分" dataDxfId="26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}" name="Table3" displayName="Table3" ref="A1:C80" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+  <autoFilter ref="A1:C80" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{9CBDF56B-3BCD-4FF2-8195-561FA1F4C31A}" name="药品ID" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{77270F8D-0C55-4EBC-B9E0-6E3C41859F9D}" name="成分" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{FC03B7AA-E421-4532-B8E6-ECB424CCAB8A}" name="ComponentEnglish" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}" name="Table5" displayName="Table5" ref="A1:B3" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
-  <autoFilter ref="A1:B3" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}" name="Table5" displayName="Table5" ref="A1:B5" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:B5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B8626E94-0403-419E-8E68-71E33A149F5F}" name="药品ID" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{69B649F7-4B8F-4BD8-8C6B-CA5943FF7F38}" name="功能" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{B8626E94-0403-419E-8E68-71E33A149F5F}" name="药品ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{69B649F7-4B8F-4BD8-8C6B-CA5943FF7F38}" name="功能" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}" name="Table4" displayName="Table4" ref="A1:B4" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:B4" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}" name="Table4" displayName="Table4" ref="A1:B5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4" totalsRowBorderDxfId="2">
+  <autoFilter ref="A1:B5" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B3E95E7E-96F3-4FFA-B777-46887DE69A33}" name="药品ID" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{65C8285F-658B-48F3-A03C-C101895E22EF}" name="主治" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{B3E95E7E-96F3-4FFA-B777-46887DE69A33}" name="药品ID" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{65C8285F-658B-48F3-A03C-C101895E22EF}" name="主治" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1316,158 +1655,1009 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C0E823-9BD2-43CB-A179-B4CF5CB62E6F}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.86328125" customWidth="1"/>
+    <col min="3" max="3" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="H1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="10" t="str">
         <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
         <v>m000001</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="G2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="10"/>
+      <c r="I2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="J2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="6" t="str">
+      <c r="B3" s="10" t="str">
         <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
         <v>m000002</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="G3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="J3" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="6" t="str">
+      <c r="B4" s="10" t="str">
         <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
         <v>m000003</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="G4" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="J4" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="6" t="str">
+      <c r="B5" s="10" t="str">
         <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
         <v>m000004</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="G5" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="10"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="10" t="str">
         <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
         <v>m000005</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="G6" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="H6" s="10"/>
+      <c r="I6" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="J6" s="2" t="s">
         <v>94</v>
       </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="7" t="str">
+        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
+        <v>m000006</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="7" t="str">
+        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
+        <v>m000007</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H7" r:id="rId1" xr:uid="{C9ED32D3-DBAA-43AD-9A4E-7FE080E5A032}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7750010-8426-4DA5-9D37-A1517A3A4563}">
+  <dimension ref="A1:C80"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11.73046875" customWidth="1"/>
+    <col min="2" max="2" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="2"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="8"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A69" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A70" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A71" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A72" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A73" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A74" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C74" s="8"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A75" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C75" s="8"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A76" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" s="8"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A77" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C77" s="8"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A78" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C78" s="8"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A79" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C79" s="8"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A80" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C80" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1478,533 +2668,52 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7750010-8426-4DA5-9D37-A1517A3A4563}">
-  <dimension ref="A1:B60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7925662C-692A-4A45-AA4F-75A27046A9CD}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7925662C-692A-4A45-AA4F-75A27046A9CD}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="15" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2017,43 +2726,51 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CA61E6-D3C1-47E8-B2E1-3DBA27FAE247}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.73046875" customWidth="1"/>
+    <col min="2" max="2" width="12.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="15" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="15" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/cn-med-kg/medicine_dataset.xlsx
+++ b/cn-med-kg/medicine_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Chinese_Medicine\cn-med-kg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C279403B-CCAA-406C-8BD8-179DD8009012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2742809D-9C4D-409F-906D-D37BE966E1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{FCBB9041-7F32-418A-9A6B-AB2AB6A56C91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FCBB9041-7F32-418A-9A6B-AB2AB6A56C91}"/>
   </bookViews>
   <sheets>
     <sheet name="1-namelist" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="190">
   <si>
     <t>药品名称</t>
   </si>
@@ -498,6 +498,117 @@
   </si>
   <si>
     <t>支气管炎咳嗽</t>
+  </si>
+  <si>
+    <t>清咽滴丸</t>
+  </si>
+  <si>
+    <t>达仁堂</t>
+  </si>
+  <si>
+    <t>津药达仁堂集团股份有限公司第六中药厂</t>
+  </si>
+  <si>
+    <t>WS3-176(Z-25)-97(Z)-2019</t>
+  </si>
+  <si>
+    <t>批准文号</t>
+  </si>
+  <si>
+    <t>国药准字Z10930004</t>
+  </si>
+  <si>
+    <t>天津市北辰区青光北</t>
+  </si>
+  <si>
+    <t>4000929666</t>
+  </si>
+  <si>
+    <t>https://www.tj6zy.com.cn</t>
+  </si>
+  <si>
+    <t>Qingyan Diwan</t>
+  </si>
+  <si>
+    <t>Hong Tie</t>
+  </si>
+  <si>
+    <t>Lao Hei Gao</t>
+  </si>
+  <si>
+    <t>Shennong Zhentonggao</t>
+  </si>
+  <si>
+    <t>MuZhiWaiFanTie</t>
+  </si>
+  <si>
+    <t>QiangLiPiPaLu</t>
+  </si>
+  <si>
+    <t>m000008</t>
+  </si>
+  <si>
+    <t>青黛</t>
+  </si>
+  <si>
+    <t>甘草</t>
+  </si>
+  <si>
+    <t>诃子</t>
+  </si>
+  <si>
+    <t>HeZi</t>
+  </si>
+  <si>
+    <t>人工牛黄</t>
+  </si>
+  <si>
+    <t>疏风清热</t>
+  </si>
+  <si>
+    <t>解毒利咽</t>
+  </si>
+  <si>
+    <t>风热喉痹，咽痛，咽干，口渴</t>
+  </si>
+  <si>
+    <t>微恶风，发热，咽部红肿，急性咽炎</t>
+  </si>
+  <si>
+    <t>草本咽喉贴</t>
+  </si>
+  <si>
+    <t>CaoBeiYanHouTie</t>
+  </si>
+  <si>
+    <t>叶向舍</t>
+  </si>
+  <si>
+    <t>南阳仲古艾业有限公司</t>
+  </si>
+  <si>
+    <t>南阳市高新区中关村科技产业聚集区纬十路18号</t>
+  </si>
+  <si>
+    <t>Q/NGZ022-2020</t>
+  </si>
+  <si>
+    <t>m000009</t>
+  </si>
+  <si>
+    <t>干姜</t>
+  </si>
+  <si>
+    <t>透骨草</t>
+  </si>
+  <si>
+    <t>辣椒</t>
+  </si>
+  <si>
+    <t>伸筋草</t>
+  </si>
+  <si>
+    <t>缓解咽部疼痛不适</t>
   </si>
 </sst>
 </file>
@@ -659,7 +770,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -675,6 +786,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -682,7 +796,22 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="36">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -743,13 +872,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -770,6 +892,13 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1284,55 +1413,56 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}" name="Table2" displayName="Table2" ref="A1:J8" totalsRowShown="0" headerRowDxfId="34" headerRowBorderDxfId="33" tableBorderDxfId="32" totalsRowBorderDxfId="31">
-  <autoFilter ref="A1:J8" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{70404F4C-EA74-419B-B8F7-C0E749DBA8EF}" name="药品名称" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{A127C5AC-1A8D-4194-B82B-CEA8C46568A9}" name="UID" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}" name="Table2" displayName="Table2" ref="A1:K10" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:K10" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{70404F4C-EA74-419B-B8F7-C0E749DBA8EF}" name="药品名称" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{A127C5AC-1A8D-4194-B82B-CEA8C46568A9}" name="UID" dataDxfId="30">
       <calculatedColumnFormula>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{745BAE8D-3E74-492D-9F1F-A46F418B7407}" name="品牌" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{4568304F-01F3-4E31-A34C-C35C96C88C80}" name="NameEnglish" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{8640C111-58A7-4B70-8A2F-6ECA558B9042}" name="BrandEnglish" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{21E7B030-7D6F-4754-8BAA-1C33EF145001}" name="生产商" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{76794CF7-5E96-4BA4-A111-0F4FB586AAEB}" name="生产商地址" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{835D09B6-5D13-418C-9FB4-33A768C770CA}" name="生产商网址" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{098A7009-4AD7-411F-A1F5-1CE1E004D519}" name="生产商电话" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{2B5D44FA-F4F3-4890-8993-4D8C1FD7AA21}" name="执行标准" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{745BAE8D-3E74-492D-9F1F-A46F418B7407}" name="品牌" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{4568304F-01F3-4E31-A34C-C35C96C88C80}" name="NameEnglish" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{8640C111-58A7-4B70-8A2F-6ECA558B9042}" name="BrandEnglish" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{21E7B030-7D6F-4754-8BAA-1C33EF145001}" name="生产商" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{76794CF7-5E96-4BA4-A111-0F4FB586AAEB}" name="生产商地址" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{835D09B6-5D13-418C-9FB4-33A768C770CA}" name="生产商网址" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{098A7009-4AD7-411F-A1F5-1CE1E004D519}" name="生产商电话" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{A8035F40-8DAA-459C-8132-AB84A20FE398}" name="批准文号" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{2B5D44FA-F4F3-4890-8993-4D8C1FD7AA21}" name="执行标准" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}" name="Table3" displayName="Table3" ref="A1:C80" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
-  <autoFilter ref="A1:C80" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}" name="Table3" displayName="Table3" ref="A1:C97" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+  <autoFilter ref="A1:C97" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9CBDF56B-3BCD-4FF2-8195-561FA1F4C31A}" name="药品ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{77270F8D-0C55-4EBC-B9E0-6E3C41859F9D}" name="成分" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{FC03B7AA-E421-4532-B8E6-ECB424CCAB8A}" name="ComponentEnglish" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{9CBDF56B-3BCD-4FF2-8195-561FA1F4C31A}" name="药品ID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{77270F8D-0C55-4EBC-B9E0-6E3C41859F9D}" name="成分" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{FC03B7AA-E421-4532-B8E6-ECB424CCAB8A}" name="ComponentEnglish" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}" name="Table5" displayName="Table5" ref="A1:B5" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
-  <autoFilter ref="A1:B5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}" name="Table5" displayName="Table5" ref="A1:B7" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+  <autoFilter ref="A1:B7" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B8626E94-0403-419E-8E68-71E33A149F5F}" name="药品ID" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{69B649F7-4B8F-4BD8-8C6B-CA5943FF7F38}" name="功能" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{B8626E94-0403-419E-8E68-71E33A149F5F}" name="药品ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{69B649F7-4B8F-4BD8-8C6B-CA5943FF7F38}" name="功能" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}" name="Table4" displayName="Table4" ref="A1:B5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4" totalsRowBorderDxfId="2">
-  <autoFilter ref="A1:B5" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}" name="Table4" displayName="Table4" ref="A1:B8" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+  <autoFilter ref="A1:B8" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B3E95E7E-96F3-4FFA-B777-46887DE69A33}" name="药品ID" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{65C8285F-658B-48F3-A03C-C101895E22EF}" name="主治" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B3E95E7E-96F3-4FFA-B777-46887DE69A33}" name="药品ID" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{65C8285F-658B-48F3-A03C-C101895E22EF}" name="主治" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1655,22 +1785,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C0E823-9BD2-43CB-A179-B4CF5CB62E6F}">
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.86328125" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.53125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.1328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="9" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1698,11 +1829,14 @@
       <c r="I1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1713,7 +1847,9 @@
       <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="10" t="s">
+        <v>163</v>
+      </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10" t="s">
         <v>5</v>
@@ -1725,11 +1861,12 @@
       <c r="I2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="16"/>
+      <c r="K2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1740,7 +1877,9 @@
       <c r="C3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="10"/>
+      <c r="D3" s="10" t="s">
+        <v>164</v>
+      </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10" t="s">
         <v>21</v>
@@ -1752,11 +1891,12 @@
       <c r="I3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="16"/>
+      <c r="K3" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -1767,7 +1907,9 @@
       <c r="C4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="10" t="s">
+        <v>165</v>
+      </c>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
         <v>39</v>
@@ -1779,11 +1921,12 @@
       <c r="I4" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="16"/>
+      <c r="K4" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>71</v>
       </c>
@@ -1794,7 +1937,9 @@
       <c r="C5" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>166</v>
+      </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10" t="s">
         <v>73</v>
@@ -1804,11 +1949,12 @@
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="16"/>
+      <c r="K5" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>88</v>
       </c>
@@ -1831,11 +1977,12 @@
       <c r="I6" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="16"/>
+      <c r="K6" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>101</v>
       </c>
@@ -1864,9 +2011,10 @@
       <c r="I7" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J7" s="17"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>139</v>
       </c>
@@ -1877,7 +2025,9 @@
       <c r="C8" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
         <v>141</v>
@@ -1887,31 +2037,95 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="14"/>
-      <c r="J8" s="8"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="7" t="str">
+        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
+        <v>m000008</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="7" t="str">
+        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
+        <v>m000009</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="8" t="s">
+        <v>183</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{C9ED32D3-DBAA-43AD-9A4E-7FE080E5A032}"/>
+    <hyperlink ref="H9" r:id="rId2" xr:uid="{DF795664-B76D-4D7C-BF90-3039B26CCFB4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7750010-8426-4DA5-9D37-A1517A3A4563}">
-  <dimension ref="A1:C80"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C97"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.73046875" customWidth="1"/>
-    <col min="2" max="2" width="18.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>100</v>
       </c>
@@ -1922,7 +2136,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
@@ -1931,7 +2145,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -1940,7 +2154,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>77</v>
       </c>
@@ -1949,7 +2163,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>77</v>
       </c>
@@ -1958,7 +2172,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>77</v>
       </c>
@@ -1967,7 +2181,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>77</v>
       </c>
@@ -1976,7 +2190,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>77</v>
       </c>
@@ -1985,7 +2199,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
@@ -1994,7 +2208,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>77</v>
       </c>
@@ -2003,7 +2217,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>77</v>
       </c>
@@ -2012,7 +2226,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>77</v>
       </c>
@@ -2021,7 +2235,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>78</v>
       </c>
@@ -2030,7 +2244,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>78</v>
       </c>
@@ -2039,7 +2253,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>78</v>
       </c>
@@ -2048,7 +2262,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>78</v>
       </c>
@@ -2057,7 +2271,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>78</v>
       </c>
@@ -2066,7 +2280,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>78</v>
       </c>
@@ -2075,7 +2289,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>78</v>
       </c>
@@ -2084,7 +2298,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>78</v>
       </c>
@@ -2093,7 +2307,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>79</v>
       </c>
@@ -2102,7 +2316,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>79</v>
       </c>
@@ -2111,7 +2325,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>79</v>
       </c>
@@ -2120,7 +2334,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>79</v>
       </c>
@@ -2129,7 +2343,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>79</v>
       </c>
@@ -2138,7 +2352,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>79</v>
       </c>
@@ -2147,7 +2361,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>79</v>
       </c>
@@ -2156,7 +2370,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>79</v>
       </c>
@@ -2165,7 +2379,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>79</v>
       </c>
@@ -2174,7 +2388,7 @@
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>79</v>
       </c>
@@ -2183,7 +2397,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>79</v>
       </c>
@@ -2192,7 +2406,7 @@
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>79</v>
       </c>
@@ -2201,7 +2415,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>79</v>
       </c>
@@ -2210,7 +2424,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>79</v>
       </c>
@@ -2219,7 +2433,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>79</v>
       </c>
@@ -2228,7 +2442,7 @@
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>79</v>
       </c>
@@ -2237,7 +2451,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>79</v>
       </c>
@@ -2246,7 +2460,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>79</v>
       </c>
@@ -2255,7 +2469,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>79</v>
       </c>
@@ -2264,7 +2478,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -2273,7 +2487,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>79</v>
       </c>
@@ -2282,7 +2496,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
@@ -2291,7 +2505,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>79</v>
       </c>
@@ -2300,7 +2514,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>79</v>
       </c>
@@ -2309,7 +2523,7 @@
       </c>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>79</v>
       </c>
@@ -2318,7 +2532,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>80</v>
       </c>
@@ -2327,7 +2541,7 @@
       </c>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>80</v>
       </c>
@@ -2336,7 +2550,7 @@
       </c>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>80</v>
       </c>
@@ -2345,7 +2559,7 @@
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>80</v>
       </c>
@@ -2354,7 +2568,7 @@
       </c>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>80</v>
       </c>
@@ -2363,7 +2577,7 @@
       </c>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>80</v>
       </c>
@@ -2372,7 +2586,7 @@
       </c>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>80</v>
       </c>
@@ -2381,7 +2595,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>80</v>
       </c>
@@ -2390,7 +2604,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>80</v>
       </c>
@@ -2399,7 +2613,7 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>89</v>
       </c>
@@ -2408,7 +2622,7 @@
       </c>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>89</v>
       </c>
@@ -2417,7 +2631,7 @@
       </c>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>89</v>
       </c>
@@ -2426,7 +2640,7 @@
       </c>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>89</v>
       </c>
@@ -2435,7 +2649,7 @@
       </c>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>89</v>
       </c>
@@ -2444,7 +2658,7 @@
       </c>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>89</v>
       </c>
@@ -2453,7 +2667,7 @@
       </c>
       <c r="C60" s="8"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>107</v>
       </c>
@@ -2464,7 +2678,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>107</v>
       </c>
@@ -2475,7 +2689,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>107</v>
       </c>
@@ -2486,7 +2700,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>107</v>
       </c>
@@ -2497,7 +2711,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>107</v>
       </c>
@@ -2508,7 +2722,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>107</v>
       </c>
@@ -2519,7 +2733,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>107</v>
       </c>
@@ -2530,7 +2744,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>107</v>
       </c>
@@ -2541,7 +2755,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>107</v>
       </c>
@@ -2552,7 +2766,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>107</v>
       </c>
@@ -2563,7 +2777,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>107</v>
       </c>
@@ -2574,7 +2788,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>107</v>
       </c>
@@ -2585,7 +2799,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>107</v>
       </c>
@@ -2596,7 +2810,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>143</v>
       </c>
@@ -2605,7 +2819,7 @@
       </c>
       <c r="C74" s="8"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>143</v>
       </c>
@@ -2614,7 +2828,7 @@
       </c>
       <c r="C75" s="8"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>143</v>
       </c>
@@ -2623,7 +2837,7 @@
       </c>
       <c r="C76" s="8"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>143</v>
       </c>
@@ -2632,7 +2846,7 @@
       </c>
       <c r="C77" s="8"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>143</v>
       </c>
@@ -2641,7 +2855,7 @@
       </c>
       <c r="C78" s="8"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
         <v>143</v>
       </c>
@@ -2650,7 +2864,7 @@
       </c>
       <c r="C79" s="8"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>143</v>
       </c>
@@ -2658,6 +2872,161 @@
         <v>61</v>
       </c>
       <c r="C80" s="8"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C81" s="8"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C82" s="8"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C84" s="8"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" s="8"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C86" s="8"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C87" s="8"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C88" s="8"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" s="8"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C90" s="8"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C91" s="8"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C92" s="8"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93" s="8"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C94" s="8"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C95" s="8"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C96" s="8"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C97" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2670,13 +3039,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7925662C-692A-4A45-AA4F-75A27046A9CD}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.73046875" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>100</v>
       </c>
@@ -2684,7 +3053,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>79</v>
       </c>
@@ -2692,7 +3061,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>79</v>
       </c>
@@ -2700,20 +3069,36 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="8" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="8" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2726,14 +3111,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CA61E6-D3C1-47E8-B2E1-3DBA27FAE247}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.73046875" customWidth="1"/>
-    <col min="2" max="2" width="12.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>100</v>
       </c>
@@ -2741,7 +3126,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>79</v>
       </c>
@@ -2749,7 +3134,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>79</v>
       </c>
@@ -2757,7 +3142,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>79</v>
       </c>
@@ -2765,12 +3150,36 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="8" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/cn-med-kg/medicine_dataset.xlsx
+++ b/cn-med-kg/medicine_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Chinese_Medicine\cn-med-kg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2742809D-9C4D-409F-906D-D37BE966E1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ACA7A5-B901-4375-B8C5-CA5E611F6B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FCBB9041-7F32-418A-9A6B-AB2AB6A56C91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FCBB9041-7F32-418A-9A6B-AB2AB6A56C91}"/>
   </bookViews>
   <sheets>
     <sheet name="1-namelist" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="219">
   <si>
     <t>药品名称</t>
   </si>
@@ -609,6 +609,93 @@
   </si>
   <si>
     <t>缓解咽部疼痛不适</t>
+  </si>
+  <si>
+    <t>丹七片</t>
+  </si>
+  <si>
+    <t>m000010</t>
+  </si>
+  <si>
+    <t>Danqi Pian</t>
+  </si>
+  <si>
+    <t>北京同仁堂科技发展股份有限公司制药厂</t>
+  </si>
+  <si>
+    <t>国药准字Z11020471</t>
+  </si>
+  <si>
+    <t>丹参</t>
+  </si>
+  <si>
+    <t>活血化瘀</t>
+  </si>
+  <si>
+    <t>血瘀气滞</t>
+  </si>
+  <si>
+    <t>心胸痹痛</t>
+  </si>
+  <si>
+    <t>眩晕头痛</t>
+  </si>
+  <si>
+    <t>经期腹痛</t>
+  </si>
+  <si>
+    <t>山药薏米莲子粥</t>
+  </si>
+  <si>
+    <t>m000011</t>
+  </si>
+  <si>
+    <t>粥之养</t>
+  </si>
+  <si>
+    <t>Zhou Zhi Yang</t>
+  </si>
+  <si>
+    <t>山东杰格郎食品有限公司</t>
+  </si>
+  <si>
+    <t>山东省临沂市沂水县崔家峪镇兖石路7号</t>
+  </si>
+  <si>
+    <t>4000096667</t>
+  </si>
+  <si>
+    <t>Q/JGL0001S</t>
+  </si>
+  <si>
+    <t>大麦仁</t>
+  </si>
+  <si>
+    <t>糯米</t>
+  </si>
+  <si>
+    <t>海藻糖</t>
+  </si>
+  <si>
+    <t>赤小豆</t>
+  </si>
+  <si>
+    <t>白扁豆</t>
+  </si>
+  <si>
+    <t>薏米</t>
+  </si>
+  <si>
+    <t>山药</t>
+  </si>
+  <si>
+    <t>芡实</t>
+  </si>
+  <si>
+    <t>莲子</t>
+  </si>
+  <si>
+    <t>枸杞</t>
   </si>
 </sst>
 </file>
@@ -770,7 +857,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -789,29 +876,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="36">
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -1158,6 +1229,21 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1308,6 +1394,7 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1413,13 +1500,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}" name="Table2" displayName="Table2" ref="A1:K10" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:K10" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}" name="Table2" displayName="Table2" ref="A1:K12" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:K12" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{70404F4C-EA74-419B-B8F7-C0E749DBA8EF}" name="药品名称" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{A127C5AC-1A8D-4194-B82B-CEA8C46568A9}" name="UID" dataDxfId="30">
-      <calculatedColumnFormula>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="7" xr3:uid="{A127C5AC-1A8D-4194-B82B-CEA8C46568A9}" name="UID" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{745BAE8D-3E74-492D-9F1F-A46F418B7407}" name="品牌" dataDxfId="29"/>
     <tableColumn id="8" xr3:uid="{4568304F-01F3-4E31-A34C-C35C96C88C80}" name="NameEnglish" dataDxfId="28"/>
     <tableColumn id="9" xr3:uid="{8640C111-58A7-4B70-8A2F-6ECA558B9042}" name="BrandEnglish" dataDxfId="27"/>
@@ -1427,42 +1512,42 @@
     <tableColumn id="5" xr3:uid="{76794CF7-5E96-4BA4-A111-0F4FB586AAEB}" name="生产商地址" dataDxfId="25"/>
     <tableColumn id="10" xr3:uid="{835D09B6-5D13-418C-9FB4-33A768C770CA}" name="生产商网址" dataDxfId="24"/>
     <tableColumn id="6" xr3:uid="{098A7009-4AD7-411F-A1F5-1CE1E004D519}" name="生产商电话" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{A8035F40-8DAA-459C-8132-AB84A20FE398}" name="批准文号" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{2B5D44FA-F4F3-4890-8993-4D8C1FD7AA21}" name="执行标准" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{A8035F40-8DAA-459C-8132-AB84A20FE398}" name="批准文号" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{2B5D44FA-F4F3-4890-8993-4D8C1FD7AA21}" name="执行标准" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}" name="Table3" displayName="Table3" ref="A1:C97" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
-  <autoFilter ref="A1:C97" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}" name="Table3" displayName="Table3" ref="A1:C110" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+  <autoFilter ref="A1:C110" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9CBDF56B-3BCD-4FF2-8195-561FA1F4C31A}" name="药品ID" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{77270F8D-0C55-4EBC-B9E0-6E3C41859F9D}" name="成分" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{FC03B7AA-E421-4532-B8E6-ECB424CCAB8A}" name="ComponentEnglish" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{9CBDF56B-3BCD-4FF2-8195-561FA1F4C31A}" name="药品ID" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{77270F8D-0C55-4EBC-B9E0-6E3C41859F9D}" name="成分" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{FC03B7AA-E421-4532-B8E6-ECB424CCAB8A}" name="ComponentEnglish" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}" name="Table5" displayName="Table5" ref="A1:B7" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
-  <autoFilter ref="A1:B7" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}" name="Table5" displayName="Table5" ref="A1:B8" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:B8" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B8626E94-0403-419E-8E68-71E33A149F5F}" name="药品ID" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{69B649F7-4B8F-4BD8-8C6B-CA5943FF7F38}" name="功能" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{B8626E94-0403-419E-8E68-71E33A149F5F}" name="药品ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{69B649F7-4B8F-4BD8-8C6B-CA5943FF7F38}" name="功能" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}" name="Table4" displayName="Table4" ref="A1:B8" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
-  <autoFilter ref="A1:B8" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}" name="Table4" displayName="Table4" ref="A1:B12" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+  <autoFilter ref="A1:B12" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B3E95E7E-96F3-4FFA-B777-46887DE69A33}" name="药品ID" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{65C8285F-658B-48F3-A03C-C101895E22EF}" name="主治" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{B3E95E7E-96F3-4FFA-B777-46887DE69A33}" name="药品ID" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{65C8285F-658B-48F3-A03C-C101895E22EF}" name="主治" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1785,7 +1870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C0E823-9BD2-43CB-A179-B4CF5CB62E6F}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -1840,9 +1925,8 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="10" t="str">
-        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
-        <v>m000001</v>
+      <c r="B2" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>3</v>
@@ -1870,9 +1954,8 @@
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="10" t="str">
-        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
-        <v>m000002</v>
+      <c r="B3" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>29</v>
@@ -1900,9 +1983,8 @@
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="10" t="str">
-        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
-        <v>m000003</v>
+      <c r="B4" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>38</v>
@@ -1930,9 +2012,8 @@
       <c r="A5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="10" t="str">
-        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
-        <v>m000004</v>
+      <c r="B5" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>72</v>
@@ -1958,9 +2039,8 @@
       <c r="A6" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="10" t="str">
-        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
-        <v>m000005</v>
+      <c r="B6" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>90</v>
@@ -1986,9 +2066,8 @@
       <c r="A7" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="7" t="str">
-        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
-        <v>m000006</v>
+      <c r="B7" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>102</v>
@@ -2018,9 +2097,8 @@
       <c r="A8" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="7" t="str">
-        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
-        <v>m000007</v>
+      <c r="B8" s="7" t="s">
+        <v>143</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>140</v>
@@ -2044,9 +2122,8 @@
       <c r="A9" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="7" t="str">
-        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
-        <v>m000008</v>
+      <c r="B9" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>154</v>
@@ -2078,9 +2155,8 @@
       <c r="A10" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B10" s="7" t="str">
-        <f>"m00000" &amp; TEXT(ROW() - ROW(Table2[[#Headers],[UID]]), "0;-0")</f>
-        <v>m000009</v>
+      <c r="B10" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>180</v>
@@ -2100,6 +2176,60 @@
       <c r="J10" s="17"/>
       <c r="K10" s="8" t="s">
         <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="J12" s="17"/>
+      <c r="K12" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2117,7 +2247,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7750010-8426-4DA5-9D37-A1517A3A4563}">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -3027,6 +3157,123 @@
         <v>36</v>
       </c>
       <c r="C97" s="8"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C98" s="8"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C99" s="8"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C100" s="8"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C101" s="8"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C102" s="8"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C103" s="8"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C104" s="8"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C105" s="8"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C106" s="8"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C107" s="8"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C108" s="8"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C109" s="8"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3039,7 +3286,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7925662C-692A-4A45-AA4F-75A27046A9CD}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -3086,19 +3333,27 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="8" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="8" t="s">
         <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3111,7 +3366,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CA61E6-D3C1-47E8-B2E1-3DBA27FAE247}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -3159,27 +3414,59 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="8" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="8" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="8" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/cn-med-kg/medicine_dataset.xlsx
+++ b/cn-med-kg/medicine_dataset.xlsx
@@ -5,18 +5,24 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Chinese_Medicine\cn-med-kg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Chinese_Medicine\cn-med-kg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ACA7A5-B901-4375-B8C5-CA5E611F6B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B6F64B-6850-41BA-844E-4C93F2EF17C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FCBB9041-7F32-418A-9A6B-AB2AB6A56C91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FCBB9041-7F32-418A-9A6B-AB2AB6A56C91}"/>
   </bookViews>
   <sheets>
     <sheet name="1-namelist" sheetId="1" r:id="rId1"/>
     <sheet name="2-component" sheetId="2" r:id="rId2"/>
     <sheet name="3-function" sheetId="3" r:id="rId3"/>
     <sheet name="4-usedfor" sheetId="4" r:id="rId4"/>
+    <sheet name="5-病脉证" sheetId="5" r:id="rId5"/>
+    <sheet name="6-方剂列表" sheetId="6" r:id="rId6"/>
+    <sheet name="7-方剂组成" sheetId="7" r:id="rId7"/>
+    <sheet name="8-出处" sheetId="8" r:id="rId8"/>
+    <sheet name="9-药味" sheetId="9" r:id="rId9"/>
+    <sheet name="9-药性" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="327">
   <si>
     <t>药品名称</t>
   </si>
@@ -696,13 +702,337 @@
   </si>
   <si>
     <t>枸杞</t>
+  </si>
+  <si>
+    <t>临床诊断</t>
+  </si>
+  <si>
+    <t>中焦湿热证</t>
+  </si>
+  <si>
+    <t>方剂名称</t>
+  </si>
+  <si>
+    <t>组分</t>
+  </si>
+  <si>
+    <t>用量</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>制法</t>
+  </si>
+  <si>
+    <t>方剂编号</t>
+  </si>
+  <si>
+    <t>fj000001</t>
+  </si>
+  <si>
+    <t>fj999999</t>
+  </si>
+  <si>
+    <t>腹泻-中焦湿热证贴</t>
+  </si>
+  <si>
+    <t>膏药</t>
+  </si>
+  <si>
+    <t>葛根</t>
+  </si>
+  <si>
+    <t>木香</t>
+  </si>
+  <si>
+    <t>槟榔</t>
+  </si>
+  <si>
+    <t>白术</t>
+  </si>
+  <si>
+    <t>克</t>
+  </si>
+  <si>
+    <t>出处</t>
+  </si>
+  <si>
+    <t>出处编号</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>作者</t>
+  </si>
+  <si>
+    <t>cc000001</t>
+  </si>
+  <si>
+    <t>伤寒杂病论</t>
+  </si>
+  <si>
+    <t>张仲景</t>
+  </si>
+  <si>
+    <t>cc999999</t>
+  </si>
+  <si>
+    <t>朝代</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>桂枝汤方</t>
+  </si>
+  <si>
+    <t>右五味，㕮（fǔ）咀。以水七升，微火煮取三升，去滓，适寒温，服一升。服已须臾，啜热稀粥一升余，以助药力，温覆令一时许，遍身漐（zhí ）漐，微似有汗者益佳，不可令如水流漓，病必不除。若一服汗出病差，停后服，不必尽剂；若不汗，更服，依前法；又不汗，后服小促役其间，半日许，令三服尽；若病重者，一日一夜服，周时观之。服一剂尽，病证犹在者，更作服；若汗不出者，乃服至二三剂。禁生冷、粘滑、肉面、五辛、酒酪、臭恶等物。</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>两</t>
+  </si>
+  <si>
+    <t>芍药</t>
+  </si>
+  <si>
+    <t>片</t>
+  </si>
+  <si>
+    <t>黄连</t>
+  </si>
+  <si>
+    <t>黄岑</t>
+  </si>
+  <si>
+    <t>大枣</t>
+  </si>
+  <si>
+    <t>枚</t>
+  </si>
+  <si>
+    <t>掰</t>
+  </si>
+  <si>
+    <t>去皮</t>
+  </si>
+  <si>
+    <t>药材</t>
+  </si>
+  <si>
+    <t>辛</t>
+  </si>
+  <si>
+    <t>热</t>
+  </si>
+  <si>
+    <t>药味</t>
+  </si>
+  <si>
+    <t>药性</t>
+  </si>
+  <si>
+    <t>苦</t>
+  </si>
+  <si>
+    <t>酸</t>
+  </si>
+  <si>
+    <t>甘</t>
+  </si>
+  <si>
+    <t>微寒</t>
+  </si>
+  <si>
+    <t>平</t>
+  </si>
+  <si>
+    <t>温</t>
+  </si>
+  <si>
+    <t>炙</t>
+  </si>
+  <si>
+    <t>切</t>
+  </si>
+  <si>
+    <t>病</t>
+  </si>
+  <si>
+    <t>脉</t>
+  </si>
+  <si>
+    <t>证</t>
+  </si>
+  <si>
+    <t>腹泻，腹痛，肠道菌群失调</t>
+  </si>
+  <si>
+    <t>对应方剂</t>
+  </si>
+  <si>
+    <t>阴阳俱浮</t>
+  </si>
+  <si>
+    <t>病脉证编号</t>
+  </si>
+  <si>
+    <t>bmz000001</t>
+  </si>
+  <si>
+    <t>bmz999999</t>
+  </si>
+  <si>
+    <t>太阳病</t>
+  </si>
+  <si>
+    <t>头痛发热，汗出恶风者</t>
+  </si>
+  <si>
+    <t>桂枝加葛根汤</t>
+  </si>
+  <si>
+    <t>fj000002</t>
+  </si>
+  <si>
+    <t>项背强几几者，反汗出恶风者</t>
+  </si>
+  <si>
+    <t>下之后，其气上冲者</t>
+  </si>
+  <si>
+    <t>bmz000002</t>
+  </si>
+  <si>
+    <t>bmz000003</t>
+  </si>
+  <si>
+    <t>bmz000004</t>
+  </si>
+  <si>
+    <t>发汗，遂漏不止，其人恶风，小便难，四支微急，难以屈伸者</t>
+  </si>
+  <si>
+    <t>fj000003</t>
+  </si>
+  <si>
+    <t>桂枝加附子汤</t>
+  </si>
+  <si>
+    <t>桂枝去芍药汤</t>
+  </si>
+  <si>
+    <t>fj000004</t>
+  </si>
+  <si>
+    <t>下之后，脉促胸满者</t>
+  </si>
+  <si>
+    <t>bmz000005</t>
+  </si>
+  <si>
+    <t>bmz000006</t>
+  </si>
+  <si>
+    <t>下之后，脉促胸满者，若微恶寒者</t>
+  </si>
+  <si>
+    <t>fj000005</t>
+  </si>
+  <si>
+    <t>桂枝去芍药加附子汤</t>
+  </si>
+  <si>
+    <t>bmz000007</t>
+  </si>
+  <si>
+    <t>得之八九日，如疟状，发热恶寒，热多寒少，其人不呕，清便欲自可，一日二三度发，脉微缓者，为欲愈也。脉微而恶寒者，此阴阳俱虚，不可更发汗、更下、更吐也。面色反有热色者，未欲解也，以其不能得小汗出，身必痒</t>
+  </si>
+  <si>
+    <t>脉微</t>
+  </si>
+  <si>
+    <t>bmz000008</t>
+  </si>
+  <si>
+    <t>bmz000009</t>
+  </si>
+  <si>
+    <t>发热而渴，不恶寒者，为温病。若发汗已，身灼热者，名曰风温。自汗出，身重，多眠睡，鼻息必鼾，语言难出</t>
+  </si>
+  <si>
+    <t>阳浮而阴弱</t>
+  </si>
+  <si>
+    <t>阳浮者，热自发；阴弱者，汗自出。啬啬恶寒，淅淅恶风，翕翕发热，鼻鸣干呕者</t>
+  </si>
+  <si>
+    <t>bmz000010</t>
+  </si>
+  <si>
+    <t>桂枝麻黄各半汤</t>
+  </si>
+  <si>
+    <t>fj000006</t>
+  </si>
+  <si>
+    <t>初服桂枝汤，反烦不解者，先刺风池、风府，却与桂枝汤则愈</t>
+  </si>
+  <si>
+    <t>益安寧丸</t>
+  </si>
+  <si>
+    <t>m000012</t>
+  </si>
+  <si>
+    <t>同溢堂</t>
+  </si>
+  <si>
+    <t>银杏叶</t>
+  </si>
+  <si>
+    <t>山楂叶</t>
+  </si>
+  <si>
+    <t>虫草菌丝体</t>
+  </si>
+  <si>
+    <t>陈皮</t>
+  </si>
+  <si>
+    <t>柿子</t>
+  </si>
+  <si>
+    <t>蜂王浆</t>
+  </si>
+  <si>
+    <t>葡萄籽提取物</t>
+  </si>
+  <si>
+    <t>补气活血</t>
+  </si>
+  <si>
+    <t>益肝健肾</t>
+  </si>
+  <si>
+    <t>养心安神</t>
+  </si>
+  <si>
+    <t>治疗气血虚弱，肝肾不足所致的胸闷气短，畏寒肢冷，手足麻木，对失眠健忘、神疲乏力、腰膝酸软也有一定疗效</t>
+  </si>
+  <si>
+    <t>Yi An Ning Pills</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -720,6 +1050,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -857,7 +1195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -876,13 +1214,896 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="85">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -1500,54 +2721,135 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}" name="Table2" displayName="Table2" ref="A1:K12" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:K12" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}" name="Table2" displayName="Table2" ref="A1:K13" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
+  <autoFilter ref="A1:K13" xr:uid="{2091243D-01EB-417B-A545-8F66A0029A2F}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{70404F4C-EA74-419B-B8F7-C0E749DBA8EF}" name="药品名称" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{A127C5AC-1A8D-4194-B82B-CEA8C46568A9}" name="UID" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{745BAE8D-3E74-492D-9F1F-A46F418B7407}" name="品牌" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{4568304F-01F3-4E31-A34C-C35C96C88C80}" name="NameEnglish" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{8640C111-58A7-4B70-8A2F-6ECA558B9042}" name="BrandEnglish" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{21E7B030-7D6F-4754-8BAA-1C33EF145001}" name="生产商" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{76794CF7-5E96-4BA4-A111-0F4FB586AAEB}" name="生产商地址" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{835D09B6-5D13-418C-9FB4-33A768C770CA}" name="生产商网址" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{098A7009-4AD7-411F-A1F5-1CE1E004D519}" name="生产商电话" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{A8035F40-8DAA-459C-8132-AB84A20FE398}" name="批准文号" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{2B5D44FA-F4F3-4890-8993-4D8C1FD7AA21}" name="执行标准" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{70404F4C-EA74-419B-B8F7-C0E749DBA8EF}" name="药品名称" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{A127C5AC-1A8D-4194-B82B-CEA8C46568A9}" name="UID" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{745BAE8D-3E74-492D-9F1F-A46F418B7407}" name="品牌" dataDxfId="78"/>
+    <tableColumn id="8" xr3:uid="{4568304F-01F3-4E31-A34C-C35C96C88C80}" name="NameEnglish" dataDxfId="77"/>
+    <tableColumn id="9" xr3:uid="{8640C111-58A7-4B70-8A2F-6ECA558B9042}" name="BrandEnglish" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{21E7B030-7D6F-4754-8BAA-1C33EF145001}" name="生产商" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{76794CF7-5E96-4BA4-A111-0F4FB586AAEB}" name="生产商地址" dataDxfId="74"/>
+    <tableColumn id="10" xr3:uid="{835D09B6-5D13-418C-9FB4-33A768C770CA}" name="生产商网址" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{098A7009-4AD7-411F-A1F5-1CE1E004D519}" name="生产商电话" dataDxfId="72"/>
+    <tableColumn id="11" xr3:uid="{A8035F40-8DAA-459C-8132-AB84A20FE398}" name="批准文号" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{2B5D44FA-F4F3-4890-8993-4D8C1FD7AA21}" name="执行标准" dataDxfId="70"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DBC86C72-3488-4660-9E82-7E0F11E075A6}" name="Table10" displayName="Table10" ref="A1:B6" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+  <autoFilter ref="A1:B6" xr:uid="{DBC86C72-3488-4660-9E82-7E0F11E075A6}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{10D8D18F-8DDE-48AE-B4F0-51DF1BFF5BC9}" name="药材" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{C317C2DB-6B5C-4C98-880C-3B5F261B0DCC}" name="药性" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}" name="Table3" displayName="Table3" ref="A1:C110" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
-  <autoFilter ref="A1:C110" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}" name="Table3" displayName="Table3" ref="A1:C119" totalsRowShown="0" headerRowDxfId="69" headerRowBorderDxfId="68" tableBorderDxfId="67" totalsRowBorderDxfId="66">
+  <autoFilter ref="A1:C119" xr:uid="{14ED46AD-AD3A-4EEB-8896-42FDC45797B6}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9CBDF56B-3BCD-4FF2-8195-561FA1F4C31A}" name="药品ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{77270F8D-0C55-4EBC-B9E0-6E3C41859F9D}" name="成分" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{FC03B7AA-E421-4532-B8E6-ECB424CCAB8A}" name="ComponentEnglish" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{9CBDF56B-3BCD-4FF2-8195-561FA1F4C31A}" name="药品ID" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{77270F8D-0C55-4EBC-B9E0-6E3C41859F9D}" name="成分" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{FC03B7AA-E421-4532-B8E6-ECB424CCAB8A}" name="ComponentEnglish" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}" name="Table5" displayName="Table5" ref="A1:B8" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
-  <autoFilter ref="A1:B8" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}" name="Table5" displayName="Table5" ref="A1:B11" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" tableBorderDxfId="59" totalsRowBorderDxfId="58">
+  <autoFilter ref="A1:B11" xr:uid="{CA49AA06-1ABA-4D07-85FE-0008DCD2BD44}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B8626E94-0403-419E-8E68-71E33A149F5F}" name="药品ID" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{69B649F7-4B8F-4BD8-8C6B-CA5943FF7F38}" name="功能" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{B8626E94-0403-419E-8E68-71E33A149F5F}" name="药品ID" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{69B649F7-4B8F-4BD8-8C6B-CA5943FF7F38}" name="功能" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}" name="Table4" displayName="Table4" ref="A1:B12" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3" totalsRowBorderDxfId="2">
-  <autoFilter ref="A1:B12" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}" name="Table4" displayName="Table4" ref="A1:B13" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+  <autoFilter ref="A1:B13" xr:uid="{959167B2-548D-49FA-94EE-4B29E8917423}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B3E95E7E-96F3-4FFA-B777-46887DE69A33}" name="药品ID" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{65C8285F-658B-48F3-A03C-C101895E22EF}" name="主治" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B3E95E7E-96F3-4FFA-B777-46887DE69A33}" name="药品ID" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{65C8285F-658B-48F3-A03C-C101895E22EF}" name="主治" dataDxfId="49"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A09D0030-5E44-4A6E-8CBD-65D7C895A859}" name="Table11" displayName="Table11" ref="A1:G12" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
+  <autoFilter ref="A1:G12" xr:uid="{A09D0030-5E44-4A6E-8CBD-65D7C895A859}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C44A1C76-EE5A-4D2B-819B-EBF1E3B6050C}" name="病脉证编号" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{E8D76948-4765-4EC1-B5B3-0D022F5265E3}" name="病" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{77F344CB-41BB-4BAB-99C0-66409360D754}" name="脉" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{7AFEF687-47F6-4F60-8831-EE0C0C3DC2FB}" name="证" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{F3477A1C-FA1A-4306-B953-3945E989FB6F}" name="对应方剂" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{DB0E14F7-372D-4BE7-A579-FB4DE0F0113C}" name="出处" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{46B5CA3B-57EC-4F86-AC5E-25BF585C55AA}" name="日期" dataDxfId="37"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{96727F20-FEC3-4F68-824E-CC57F8211275}" name="Table7" displayName="Table7" ref="A1:D8" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="35" tableBorderDxfId="34" totalsRowBorderDxfId="33">
+  <autoFilter ref="A1:D8" xr:uid="{96727F20-FEC3-4F68-824E-CC57F8211275}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{5641B603-F66B-4834-84A5-8D17D205F90C}" name="方剂编号" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{4C56F6B7-083E-46F2-8828-CFB235FCFD27}" name="方剂名称" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{60637B3F-A3B1-43F9-BF7B-2F96DF1663E6}" name="制法" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{229EC401-52B4-4354-9CD9-3AD7461991E9}" name="出处" dataDxfId="29"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8689EDB3-DA97-456E-BFC3-61A22278591A}" name="Table6" displayName="Table6" ref="A1:E13" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+  <autoFilter ref="A1:E13" xr:uid="{8689EDB3-DA97-456E-BFC3-61A22278591A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E13">
+    <sortCondition ref="A1:A13"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{9E912DF6-51F3-4D82-9F50-3EE93AE90F8A}" name="方剂编号" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{1607F7D4-6AA7-49F1-A07A-B297EE6D3BB3}" name="组分" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{D18A3CD4-B216-4FF4-8D84-353CDC04A2D4}" name="备注" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{126333F1-CB1E-4663-9D3F-E1A4193F4EAE}" name="用量" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{3539DA45-BC18-48D1-87C7-C3B6A725F6C9}" name="单位" dataDxfId="20"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E68B9124-7C18-41ED-99D4-BB7A57A76969}" name="Table8" displayName="Table8" ref="A1:D3" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+  <autoFilter ref="A1:D3" xr:uid="{E68B9124-7C18-41ED-99D4-BB7A57A76969}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{699F6A11-5F52-4C9A-B31C-9E0CB9EE0B77}" name="出处编号" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{D8024A9A-1CC5-4D52-97E1-89FC7EED2DE3}" name="名称" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{72149739-255E-4AF7-B886-072345FAB497}" name="作者" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{DE0183FC-F378-4817-9CE2-C7E721B0FCD5}" name="朝代" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{49B8567F-6962-41EB-B49F-1CE2D36668F5}" name="Table9" displayName="Table9" ref="A1:B7" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:B7" xr:uid="{49B8567F-6962-41EB-B49F-1CE2D36668F5}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{5970408D-70C4-46D6-BFB3-BB27C244D262}" name="药材" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{54D7AB47-428A-4495-BA37-3DA35ADD4A76}" name="药味" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1870,7 +3172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C0E823-9BD2-43CB-A179-B4CF5CB62E6F}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -2207,7 +3509,7 @@
       <c r="A12" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -2231,6 +3533,27 @@
       <c r="K12" s="8" t="s">
         <v>208</v>
       </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2245,9 +3568,70 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394F92F3-86CD-46BA-8211-3CBBA85E6982}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7750010-8426-4DA5-9D37-A1517A3A4563}">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -3274,6 +4658,87 @@
         <v>218</v>
       </c>
       <c r="C110" s="8"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C111" s="8"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="C112" s="8"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C113" s="8"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C114" s="8"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C115" s="8"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C116" s="8"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C117" s="8"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="C118" s="8"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C119" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3286,7 +4751,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7925662C-692A-4A45-AA4F-75A27046A9CD}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -3354,6 +4819,30 @@
       </c>
       <c r="B8" s="8" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3366,7 +4855,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CA61E6-D3C1-47E8-B2E1-3DBA27FAE247}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -3467,6 +4956,744 @@
       </c>
       <c r="B12" s="8" t="s">
         <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>325</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098F12C2-AEF8-4296-9EC5-414E51ED4030}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="18">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G12" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF583D11-8ECB-49E4-9BA7-817CA39508C0}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C5492A4-E2D6-4241-860C-1060C5217042}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D2" s="10">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" s="10">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="10">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7">
+        <v>3</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7">
+        <v>3</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="7">
+        <v>6</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D11" s="7">
+        <v>4</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D12" s="7">
+        <v>6</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7">
+        <v>5</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07C24F6-6EA7-4CE7-AAA3-B497845B8EDA}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2CDD0B-9304-4798-8377-E10607B78F3F}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
